--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1430</v>
+        <v>1904</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>986</v>
+        <v>1321</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>258</v>
+        <v>370</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>182</v>
+        <v>249</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06621</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASSINO</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>06621</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>CASSINO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,51 +1087,51 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1199,47 +1199,47 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,39 +1249,39 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>07270</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>CAMPOBASSO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>07270</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CAMPOBASSO</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,39 +1465,39 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>9</v>
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I25" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="M25" s="12" t="n">
         <v>35</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>21</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1685,47 +1685,47 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,32 +1735,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -1774,17 +1774,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06711</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TERRACINA</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H29" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="K29" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1828,54 +1828,54 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>06711</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>TERRACINA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1901,35 +1901,35 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>2</v>
@@ -1979,42 +1979,42 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06520</t>
+          <t>06607</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SULMONA</t>
+          <t>SAN SALVO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J33" s="12" t="n">
         <v>0</v>
       </c>
@@ -2022,45 +2022,45 @@
         <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06883</t>
+          <t>06520</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PESCARA</t>
+          <t>SULMONA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>0</v>
@@ -2079,38 +2079,38 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06892</t>
+          <t>06883</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MANOPPELLO</t>
+          <t>PESCARA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
@@ -2129,19 +2129,19 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06607</t>
+          <t>06892</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SAN SALVO</t>
+          <t>MANOPPELLO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>162</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.02469135802469136</v>
+        <v>4</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>137</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.489051094890511</v>
+        <v>67</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>151</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.2052980132450331</v>
+        <v>31</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>122</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.03278688524590164</v>
+        <v>4</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>118</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.02542372881355932</v>
+        <v>3</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>107</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.02803738317757009</v>
+        <v>3</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>47</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.2127659574468085</v>
+        <v>10</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>71</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.2816901408450704</v>
+        <v>20</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>37</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>82</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.01219512195121951</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>102</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.08823529411764706</v>
+        <v>9</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>66</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5303030303030303</v>
+        <v>35</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>59</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.05084745762711865</v>
+        <v>3</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1904</v>
+        <v>2018</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1321</v>
+        <v>1399</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>35</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>4</v>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>3</v>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H16" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K16" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>40</v>
-      </c>
       <c r="L16" s="12" t="n">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,35 +1249,35 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>5</v>
@@ -1427,16 +1427,16 @@
         <v>6</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>1</v>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>4</v>
@@ -1481,23 +1481,23 @@
         <v>3</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1523,35 +1523,35 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>23</v>
@@ -1598,10 +1598,10 @@
         <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>30</v>
@@ -1643,23 +1643,23 @@
         <v>3</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>35</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>3</v>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F28" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="I28" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1828,108 +1828,108 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>06711</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>TERRACINA</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>06711</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>TERRACINA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
         <v>36</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0</v>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -1944,7 +1944,11 @@
           <t>PENNE</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
@@ -1994,7 +1998,11 @@
           <t>SAN SALVO</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>
@@ -2044,7 +2052,11 @@
           <t>SULMONA</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>COLOZZA STEFANO</t>
@@ -2094,7 +2106,11 @@
           <t>PESCARA</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
@@ -2144,7 +2160,11 @@
           <t>MANOPPELLO</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2018</v>
+        <v>2142</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1399</v>
+        <v>1478</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="H13" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>126</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>169</v>
+      </c>
+      <c r="M13" s="12" t="n">
         <v>35</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>118</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>161</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>32</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>40</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>36</v>
@@ -1004,10 +1004,10 @@
         <v>30</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>3</v>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>14</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>3</v>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,39 +1249,39 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>2</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>9</v>
@@ -1382,26 +1382,26 @@
         <v>45</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>07270</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CAMPOBASSO</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H22" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="J22" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="K22" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>07270</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>CAMPOBASSO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,32 +1465,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J23" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K23" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K23" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="L23" s="12" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>1</v>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,39 +1519,39 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
         <v>63</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>23</v>
@@ -1598,10 +1598,10 @@
         <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>5</v>
@@ -1643,23 +1643,23 @@
         <v>3</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1685,16 +1685,16 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>37</v>
@@ -1703,10 +1703,10 @@
         <v>10</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>3</v>
@@ -1739,28 +1739,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>38</v>
@@ -1805,7 +1805,7 @@
         <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>12</v>
@@ -1814,14 +1814,14 @@
         <v>2</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>69</v>
@@ -1859,16 +1859,16 @@
         <v>5</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>36</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>30</v>
@@ -1922,7 +1922,7 @@
         <v>4</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2030,14 +2030,14 @@
         <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2142</v>
+        <v>2278</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1478</v>
+        <v>1575</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>06621</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>CASSINO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,51 +979,51 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06621</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASSINO</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,35 +1033,35 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>18</v>
@@ -1166,10 +1166,10 @@
         <v>48</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="K18" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L18" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="L18" s="12" t="n">
-        <v>75</v>
-      </c>
       <c r="M18" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,39 +1249,39 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>2</v>
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>45</v>
@@ -1379,17 +1379,17 @@
         <v>9</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>14</v>
@@ -1469,35 +1469,35 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>4</v>
@@ -1535,7 +1535,7 @@
         <v>3</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>19</v>
@@ -1544,7 +1544,7 @@
         <v>4</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>1</v>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>23</v>
@@ -1598,10 +1598,10 @@
         <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,47 +1631,47 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,39 +1735,39 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1796,13 +1796,13 @@
         <v>42</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>38</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
         <v>40</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>7</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -1901,19 +1901,19 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>41</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>9</v>
@@ -1922,7 +1922,7 @@
         <v>4</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>0</v>
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>1</v>
@@ -2030,14 +2030,14 @@
         <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0</v>
@@ -2120,13 +2120,13 @@
         <v>0</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2278</v>
+        <v>2389</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1575</v>
+        <v>1653</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>452</v>
+        <v>488</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>6</v>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>36</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>21</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>145</v>
+        <v>76</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,39 +1087,39 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>37</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>4</v>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F18" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="L18" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G18" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>53</v>
-      </c>
       <c r="M18" s="12" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,39 +1249,39 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>2</v>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G21" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>137</v>
+      </c>
+      <c r="M21" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H21" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>53</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>1</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>4</v>
@@ -1535,19 +1535,19 @@
         <v>3</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>67</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>17</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>1</v>
@@ -1685,31 +1685,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>17</v>
@@ -1751,16 +1751,16 @@
         <v>29</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>3</v>
@@ -1796,7 +1796,7 @@
         <v>42</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>5</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
@@ -1859,7 +1859,7 @@
         <v>5</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>13</v>
@@ -1868,7 +1868,7 @@
         <v>7</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -1901,16 +1901,16 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>31</v>
@@ -1919,10 +1919,10 @@
         <v>9</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -2030,14 +2030,14 @@
         <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -2052,11 +2052,7 @@
           <t>SULMONA</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C34" s="2" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>COLOZZA STEFANO</t>
@@ -2106,11 +2102,7 @@
           <t>PESCARA</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
@@ -2160,11 +2152,7 @@
           <t>MANOPPELLO</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N36" headerRowCount="1">
-  <autoFilter ref="A10:N36"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O36" headerRowCount="1">
+  <autoFilter ref="A10:O36"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIA MARCO TULLIO CICERONE  33/35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Funari Emanuele</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>302</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>CONTRADA S. LIBERATA SS 16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>308</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>VIA XXII MAGGIO 1944</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>219</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>VIA CASILINA SUD KM 140+200</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="M15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIALE DELLA CROCE ROSSA 42/D</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>COLOZZA STEFANO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>V.LE ADRIATICO 168 SS259 KM 1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>S.S. 80 KM. 93 + 490</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>RACCORDO AUTOSOLE</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>CORSO MAZZINI</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>VIA NAZIONALE SUD 617</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>IV NOVEMBRE</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>COLOZZA STEFANO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>53</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>24</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>24</v>
       </c>
       <c r="L23" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>SS 80 KM 77+842</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>SS NETTUNENSE KM 21</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Funari Emanuele</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>PROSPERI CHIARA</t>
         </is>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>67</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>67</v>
       </c>
       <c r="G25" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>COLOZZA STEFANO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>46</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>17</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L26" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M26" s="12" t="n">
         <v>129</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>ISONZO</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>PROSPERI CHIARA</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>VIA CASILINA KM 104+320</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>40</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>11</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>S.P. LEUCIANA KM 2+670</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="M29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>SS 430 KM 0.525</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>VIA ROMA SNC</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>Funari Emanuele</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>PROSPERI CHIARA</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>VIA G. ROSSA</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>FRAZ-MARINELLE</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="M33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2052,27 +2183,29 @@
           <t>SULMONA</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>VIALE DELLA REPUBBLICA 8</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>COLOZZA STEFANO</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J34" s="12" t="n">
         <v>0</v>
       </c>
@@ -2085,7 +2218,10 @@
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2102,27 +2238,29 @@
           <t>PESCARA</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr"/>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>SS-5 KM-231+700</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J35" s="12" t="n">
         <v>0</v>
       </c>
@@ -2135,7 +2273,10 @@
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2152,21 +2293,23 @@
           <t>MANOPPELLO</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>STR-ST-5 TIBURTINA</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
@@ -2185,7 +2328,10 @@
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2389</v>
+        <v>2499</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1653</v>
+        <v>1723</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,52 +842,52 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>46</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ORTONA</t>
+          <t>CITTÀ SANT'ANGELO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CONTRADA S. LIBERATA SS 16</t>
+          <t>VIA XXII MAGGIO 1944</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -897,56 +897,56 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>308</v>
+        <v>223</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26869</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CITTÀ SANT'ANGELO</t>
+          <t>ORTONA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA XXII MAGGIO 1944</t>
+          <t>CONTRADA S. LIBERATA SS 16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,39 +956,39 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>219</v>
+        <v>314</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>13</v>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>90</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>10</v>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>37</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>27</v>
@@ -1394,7 +1394,7 @@
         <v>20</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>2</v>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>106</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>99</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>2</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>7</v>
@@ -1680,23 +1680,23 @@
         <v>20</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>50</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>5</v>
@@ -1739,40 +1739,40 @@
         <v>4</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ISONZO</t>
+          <t>VIA CASILINA KM 104+320</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 104+320</t>
+          <t>ISONZO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,39 +1841,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>13</v>
@@ -1984,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>9</v>
@@ -2043,7 +2043,7 @@
         <v>5</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>2</v>
@@ -2161,14 +2161,14 @@
         <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2499</v>
+        <v>2608</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1723</v>
+        <v>1796</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,52 +842,52 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>26869</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CITTÀ SANT'ANGELO</t>
+          <t>ORTONA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA XXII MAGGIO 1944</t>
+          <t>CONTRADA S. LIBERATA SS 16</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -897,56 +897,56 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>223</v>
+        <v>332</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="L12" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>194</v>
+      </c>
+      <c r="N12" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="M12" s="12" t="n">
-        <v>192</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ORTONA</t>
+          <t>CITTÀ SANT'ANGELO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CONTRADA S. LIBERATA SS 16</t>
+          <t>VIA XXII MAGGIO 1944</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,56 +956,56 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>314</v>
+        <v>229</v>
       </c>
       <c r="H13" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="I13" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>49</v>
-      </c>
       <c r="J13" s="12" t="n">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06621</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASSINO</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA SUD KM 140+200</t>
+          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,56 +1015,56 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>06621</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>CASSINO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
+          <t>VIA CASILINA SUD KM 140+200</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,39 +1074,39 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>13</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>4</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>10</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>2</v>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
+          <t>VIA NAZIONALE SUD 617</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,56 +1428,56 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SUD 617</t>
+          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I22" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>157</v>
+      </c>
+      <c r="N22" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="N22" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>7</v>
@@ -1562,23 +1562,23 @@
         <v>10</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K23" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L23" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L23" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="M23" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         <v>75</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>5</v>
@@ -1630,7 +1630,7 @@
         <v>9</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>2</v>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>20</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>5</v>
@@ -1739,16 +1739,16 @@
         <v>4</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>3</v>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>16</v>
@@ -1866,7 +1866,7 @@
         <v>12</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>1</v>
@@ -1966,13 +1966,13 @@
         <v>42</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>33</v>
@@ -1984,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2102,14 +2102,14 @@
         <v>0</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2140,19 +2140,19 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>1</v>
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
@@ -2198,13 +2198,13 @@
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2608</v>
+        <v>2742</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1796</v>
+        <v>1872</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>562</v>
+        <v>603</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>101</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>37</v>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>24</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>7</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G16" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M16" s="12" t="n">
         <v>171</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>111</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>166</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>13</v>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>V.LE ADRIATICO 168 SS259 KM 1</t>
+          <t>S.S. 80 KM. 93 + 490</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>161</v>
+        <v>207</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>148</v>
+        <v>99</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>S.S. 80 KM. 93 + 490</t>
+          <t>V.LE ADRIATICO 168 SS259 KM 1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         <v>124</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>97</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>100</v>
@@ -1335,7 +1335,7 @@
         <v>25</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>10</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>48</v>
@@ -1450,17 +1450,17 @@
         <v>10</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1494,10 +1494,10 @@
         <v>114</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>22</v>
@@ -1512,14 +1512,14 @@
         <v>33</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>7</v>
@@ -1562,19 +1562,19 @@
         <v>10</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,118 +1585,118 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>APRILIA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SS 80 KM 77+842</t>
+          <t>SS NETTUNENSE KM 21</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>APRILIA</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS NETTUNENSE KM 21</t>
+          <t>SS 80 KM 77+842</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="H25" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L25" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="M25" s="12" t="n">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1730,10 +1730,10 @@
         <v>66</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>4</v>
@@ -1748,14 +1748,14 @@
         <v>17</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>3</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>1</v>
@@ -1880,59 +1880,59 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>06711</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>TERRACINA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>S.P. LEUCIANA KM 2+670</t>
+          <t>VIA ROMA SNC</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>13</v>
@@ -1984,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
@@ -1998,59 +1998,59 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>06711</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TERRACINA</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA SNC</t>
+          <t>S.P. LEUCIANA KM 2+670</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2742</v>
+        <v>2858</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1872</v>
+        <v>1964</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>603</v>
+        <v>650</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>6</v>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>43</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>37</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06621</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASSINO</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA SUD KM 140+200</t>
+          <t>VIALE DELLA CROCE ROSSA 42/D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,35 +1074,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>06621</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>CASSINO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELLA CROCE ROSSA 42/D</t>
+          <t>VIA CASILINA SUD KM 140+200</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,35 +1133,35 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>26</v>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>66</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>4</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>10</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>77</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>3</v>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>23</v>
@@ -1444,16 +1444,16 @@
         <v>20</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>1</v>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>22</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>2</v>
@@ -1612,13 +1612,13 @@
         <v>80</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>64</v>
@@ -1630,7 +1630,7 @@
         <v>17</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>54</v>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1727,35 +1727,35 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G26" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" s="12" t="n">
         <v>49</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>48</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>3</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>1</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>52</v>
@@ -1913,10 +1913,10 @@
         <v>12</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>9</v>
@@ -1925,10 +1925,10 @@
         <v>11</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
@@ -1984,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
@@ -2025,7 +2025,7 @@
         <v>42</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>5</v>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>2</v>
@@ -2161,14 +2161,14 @@
         <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2858</v>
+        <v>2977</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1964</v>
+        <v>2046</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>650</v>
+        <v>698</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>6</v>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>43</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>37</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>46</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>66</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>4</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>10</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>3</v>
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>20</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>10</v>
@@ -1453,7 +1453,7 @@
         <v>76</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>1</v>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>8</v>
@@ -1562,16 +1562,16 @@
         <v>10</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>31</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>2</v>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>6</v>
@@ -1680,16 +1680,16 @@
         <v>6</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1727,35 +1727,35 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>3</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>1</v>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>2</v>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
@@ -1975,16 +1975,16 @@
         <v>7</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
@@ -2025,7 +2025,7 @@
         <v>42</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>5</v>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>2</v>
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2198,13 +2198,13 @@
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2977</v>
+        <v>3118</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2046</v>
+        <v>2142</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>698</v>
+        <v>757</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>140</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>64</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>39</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>35</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>46</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>4</v>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO AUTOSOLE</t>
+          <t>CORSO MAZZINI</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CORSO MAZZINI</t>
+          <t>RACCORDO AUTOSOLE</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SUD 617</t>
+          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,56 +1428,56 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>104</v>
+        <v>192</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
+          <t>VIA NAZIONALE SUD 617</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J23" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>71</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>67</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>2</v>
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>23</v>
@@ -1627,13 +1627,13 @@
         <v>29</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>6</v>
@@ -1680,16 +1680,16 @@
         <v>6</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>7</v>
@@ -1739,23 +1739,23 @@
         <v>7</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>48</v>
@@ -1863,10 +1863,10 @@
         <v>17</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>1</v>
@@ -1907,7 +1907,7 @@
         <v>51</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>14</v>
@@ -1925,14 +1925,14 @@
         <v>11</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>14</v>
@@ -1984,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
@@ -2025,7 +2025,7 @@
         <v>42</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>5</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>06607</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>PENNE</t>
+          <t>SAN SALVO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA G. ROSSA</t>
+          <t>FRAZ-MARINELLE</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,11 +2077,11 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="12" t="n">
         <v>16</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06607</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SAN SALVO</t>
+          <t>PENNE</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-MARINELLE</t>
+          <t>VIA G. ROSSA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,32 +2136,32 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3118</v>
+        <v>3270</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2142</v>
+        <v>2239</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>757</v>
+        <v>817</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>47</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>39</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>21</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>9</v>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>4</v>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CORSO MAZZINI</t>
+          <t>RACCORDO AUTOSOLE</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>118</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO AUTOSOLE</t>
+          <t>CORSO MAZZINI</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>1</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>2</v>
@@ -1585,118 +1585,118 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>APRILIA</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SS NETTUNENSE KM 21</t>
+          <t>SS 80 KM 77+842</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>113</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>APRILIA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS 80 KM 77+842</t>
+          <t>SS NETTUNENSE KM 21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>7</v>
@@ -1739,7 +1739,7 @@
         <v>7</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>20</v>
@@ -1748,14 +1748,14 @@
         <v>22</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="G27" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>67</v>
-      </c>
       <c r="H27" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1848,13 +1848,13 @@
         <v>65</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>48</v>
@@ -1866,10 +1866,10 @@
         <v>15</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,55 +1880,55 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06711</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TERRACINA</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA SNC</t>
+          <t>SS 430 KM 0.525</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,55 +1939,55 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>06711</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>TERRACINA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SS 430 KM 0.525</t>
+          <t>VIA ROMA SNC</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2102,14 +2102,14 @@
         <v>0</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2161,14 +2161,14 @@
         <v>0</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - MAGLIO EMANUELE.xlsx
@@ -684,13 +684,13 @@
         <v>26</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3270</v>
+        <v>3246</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2239</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>817</v>
+        <v>800</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>74</v>
@@ -854,7 +854,7 @@
         <v>63</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>108</v>
@@ -863,7 +863,7 @@
         <v>148</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>7</v>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>108</v>
@@ -922,10 +922,10 @@
         <v>97</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>75</v>
@@ -981,10 +981,10 @@
         <v>122</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>56</v>
@@ -1031,7 +1031,7 @@
         <v>40</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>63</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>34</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>62</v>
@@ -1099,7 +1099,7 @@
         <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>21</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>13</v>
@@ -1149,7 +1149,7 @@
         <v>46</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>27</v>
@@ -1158,7 +1158,7 @@
         <v>66</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>9</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>25</v>
@@ -1217,10 +1217,10 @@
         <v>96</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>23</v>
@@ -1276,7 +1276,7 @@
         <v>71</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>4</v>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>118</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>171</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>57</v>
@@ -1335,7 +1335,7 @@
         <v>34</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>10</v>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>38</v>
@@ -1394,7 +1394,7 @@
         <v>24</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>3</v>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>28</v>
@@ -1444,7 +1444,7 @@
         <v>35</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>18</v>
@@ -1453,7 +1453,7 @@
         <v>43</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>29</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="G22" s="12" t="n">
-        <v>140</v>
-      </c>
       <c r="H22" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>23</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>13</v>
@@ -1512,7 +1512,7 @@
         <v>81</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>1</v>
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>34</v>
@@ -1571,7 +1571,7 @@
         <v>35</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>2</v>
@@ -1585,114 +1585,114 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>16720</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>APRILIA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SS 80 KM 77+842</t>
+          <t>SS NETTUNENSE KM 21</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>APRILIA</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS NETTUNENSE KM 21</t>
+          <t>SS 80 KM 77+842</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>7</v>
@@ -1739,7 +1739,7 @@
         <v>7</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>20</v>
@@ -1748,7 +1748,7 @@
         <v>22</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>47</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>17</v>
@@ -1807,7 +1807,7 @@
         <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>13</v>
@@ -1857,7 +1857,7 @@
         <v>78</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>17</v>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>1</v>
@@ -1916,7 +1916,7 @@
         <v>7</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>15</v>
@@ -1925,7 +1925,7 @@
         <v>12</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>11</v>
@@ -1984,7 +1984,7 @@
         <v>11</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>2</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>49</v>
@@ -2034,7 +2034,7 @@
         <v>9</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>12</v>
@@ -2043,14 +2043,14 @@
         <v>2</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>6</v>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>3</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
